--- a/АБК/Том СКУД АБК/Протокол сопротивления изоляции СКУД АБК (образец и бланк).xlsx
+++ b/АБК/Том СКУД АБК/Протокол сопротивления изоляции СКУД АБК (образец и бланк).xlsx
@@ -608,7 +608,7 @@
     <row r="10" ht="26" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Исполнительная документация: 16/1/26-ИД-АБК, лист 4; кабельный журнал 16/1/26-ИД-АБК.КЖ (раздел СКУД). Рабочая документация 16/1/26-СКУД-Р.</t>
+          <t>Исполнительная документация: 16/1/26-СКУД-ИД-АБК, лист 2; кабельный журнал 16/1/26-СКУД-ИД-АБК.КЖ. Рабочая документация 16/1/26-СКУД-Р.</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1667,7 @@
     <row r="9" ht="26" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Исполнительная документация: 16/1/26-ИД-АБК, лист 4; кабельный журнал 16/1/26-ИД-АБК.КЖ (раздел СКУД). Рабочая документация 16/1/26-СКУД-Р.</t>
+          <t>Исполнительная документация: 16/1/26-СКУД-ИД-АБК, лист 2; кабельный журнал 16/1/26-СКУД-ИД-АБК.КЖ. Рабочая документация 16/1/26-СКУД-Р.</t>
         </is>
       </c>
     </row>
